--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\marinboard\BOM_schematic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\marinboard\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C506664C-F9D1-4710-B000-E99A43D1F7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE498B0-1EE6-4E0D-AF50-344C59DE315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5803721C-F8C9-41F6-8A44-40A526ECC638}"/>
   </bookViews>
@@ -539,5 +539,6 @@
     <hyperlink ref="D7" r:id="rId3" xr:uid="{BA65039C-6940-46DD-9CDE-4CBE06344117}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>